--- a/business_forms/049_restaurant_operating_expense_control--business_forms.xlsx
+++ b/business_forms/049_restaurant_operating_expense_control--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_1</t>
+          <t>restaurant_operating_expense_control_food_cost</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Operating Expense</t>
+          <t>Food Cost</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_2</t>
+          <t>restaurant_operating_expense_control_labor_cost</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Food Cost</t>
+          <t>Labor Cost</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_3</t>
+          <t>restaurant_operating_expense_control_occupancy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Food Cost %</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_4</t>
+          <t>restaurant_operating_expense_control_other_operating_expense</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Labor Cost</t>
+          <t>Other Operating Expense</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_5</t>
+          <t>restaurant_operating_expense_control_other_income</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Labor Cost %</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_6</t>
+          <t>restaurant_operating_expense_control_other_expense</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Other Expense</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_7</t>
+          <t>restaurant_operating_expense_control_depreciation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Occupancy %</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_8</t>
+          <t>restaurant_operating_expense_control_amortization</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other Operating Expense</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_9</t>
+          <t>restaurant_operating_expense_control_interest</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Other Operating Expense %</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_10</t>
+          <t>restaurant_operating_expense_control_taxes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Taxes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_11</t>
+          <t>restaurant_operating_expense_control_other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Other Income %</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_12</t>
+          <t>restaurant_operating_expense_control_food_cost_percentage</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other Expense</t>
+          <t>Food Cost Percentage</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_13</t>
+          <t>restaurant_operating_expense_control_labor_cost_percentage</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Other Expense %</t>
+          <t>Labor Cost Percentage</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_14</t>
+          <t>restaurant_operating_expense_control_occupancy_percentage</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Occupancy Percentage</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_15</t>
+          <t>restaurant_operating_expense_control_other_operating_expense_percentage</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Depreciation %</t>
+          <t>Other Operating Expense Percentage</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_16</t>
+          <t>restaurant_operating_expense_control_other_income_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Restaurant Operating Expense Control Other Income 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_17</t>
+          <t>restaurant_operating_expense_control_other_expense_percentage</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Amortization %</t>
+          <t>Other Expense Percentage</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_18</t>
+          <t>restaurant_operating_expense_control_depreciation_percentage</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Depreciation Percentage</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_19</t>
+          <t>restaurant_operating_expense_control_amortization_percentage</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Interest %</t>
+          <t>Amortization Percentage</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_20</t>
+          <t>restaurant_operating_expense_control_interest_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>Restaurant Operating Expense Control Interest 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_21</t>
+          <t>restaurant_operating_expense_control_taxes_percentage</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Taxes %</t>
+          <t>Taxes Percentage</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,44 +998,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_22</t>
+          <t>restaurant_operating_expense_control_other_percentage</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Restaurant Operating Expense Control Other Percentage</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>restaurant_operating_expense_control_fields_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Other %</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1052,12 +1029,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1080,109 +1057,109 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_2_choices</t>
+          <t>restaurant_operating_expense_control_food_cost_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_2_choices</t>
+          <t>restaurant_operating_expense_control_food_cost_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_4_choices</t>
+          <t>restaurant_operating_expense_control_labor_cost_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_4_choices</t>
+          <t>restaurant_operating_expense_control_labor_cost_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_6_choices</t>
+          <t>restaurant_operating_expense_control_occupancy_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_6_choices</t>
+          <t>restaurant_operating_expense_control_occupancy_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_8_choices</t>
+          <t>restaurant_operating_expense_control_other_operating_expense_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1199,7 +1176,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_8_choices</t>
+          <t>restaurant_operating_expense_control_other_operating_expense_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1216,238 +1193,306 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_10_choices</t>
+          <t>restaurant_operating_expense_control_other_income_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_10_choices</t>
+          <t>restaurant_operating_expense_control_other_income_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_12_choices</t>
+          <t>restaurant_operating_expense_control_other_expense_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_12_choices</t>
+          <t>restaurant_operating_expense_control_other_expense_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_14_choices</t>
+          <t>restaurant_operating_expense_control_depreciation_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_14_choices</t>
+          <t>restaurant_operating_expense_control_depreciation_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_16_choices</t>
+          <t>restaurant_operating_expense_control_amortization_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_16_choices</t>
+          <t>restaurant_operating_expense_control_amortization_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_18_choices</t>
+          <t>restaurant_operating_expense_control_interest_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_18_choices</t>
+          <t>restaurant_operating_expense_control_interest_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_20_choices</t>
+          <t>restaurant_operating_expense_control_taxes_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_20_choices</t>
+          <t>restaurant_operating_expense_control_taxes_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_22_choices</t>
+          <t>restaurant_operating_expense_control_other_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>restaurant_operating_expense_control_fields_22_choices</t>
+          <t>restaurant_operating_expense_control_other_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>restaurant_operating_expense_control_other_income_2_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>restaurant_operating_expense_control_other_income_2_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>restaurant_operating_expense_control_interest_2_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>restaurant_operating_expense_control_interest_2_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Option B</t>
         </is>
       </c>
     </row>
